--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36595.96</v>
+        <v>36230.73</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>63996.54</v>
+        <v>63646.74</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4742.61</v>
+        <v>4695.42</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>267.42</v>
+        <v>266.46</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55388.62</v>
+        <v>55268.75</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38880.85</v>
+        <v>38796.71</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>49893.06</v>
+        <v>49177.93</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43339.16</v>
+        <v>43733.36</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1064.94</v>
+        <v>1074.43</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45514.52</v>
+        <v>45193.32</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>120893.31</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>33524.29</v>
+        <v>32863.15</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>972.2</v>
+        <v>953.03</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>49153.92</v>
+        <v>49358.2</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2940.24</v>
+        <v>2965.19</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11135.63</v>
+        <v>11230.14</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2194.04</v>
+        <v>2200.95</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5896.95</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45745.39</v>
+        <v>46086.2</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>46816.76</v>
+        <v>47255.86</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>159.84</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>553.47</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>48411.56</v>
+        <v>48166.32</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5237.14</v>
+        <v>5249.15</v>
       </c>
     </row>
     <row r="26">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7077.39</v>
+        <v>7124.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>1660-651-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>18141.5</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="28">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14763.1</v>
+        <v>14591.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>1057438-184-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>26476.78</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>42647.55</v>
+        <v>42411.12</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>24022.66</v>
+        <v>23889.48</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>75136.17</v>
+        <v>74719.62</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>42965.94</v>
+        <v>42727.74</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,129 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12887.17</v>
+        <v>12973.43</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2147-386-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>5722.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1057438-237-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>14477.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079505-1159-CM25</t>
+          <t>707418-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36230.73</v>
+        <v>35614.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3532-156-CM25</t>
+          <t>1057440-268-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>63646.74</v>
+        <v>61394.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>895-80-CM25</t>
+          <t>931-101-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4695.42</v>
+        <v>3135.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>895-81-CM25</t>
+          <t>895-53-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>266.46</v>
+        <v>5929.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3532-169-CM25</t>
+          <t>1079505-1021-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55268.75</v>
+        <v>38551.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079505-1281-CM25</t>
+          <t>1079505-1159-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38796.71</v>
+        <v>36230.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079505-13-CM26</t>
+          <t>3532-156-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>49177.93</v>
+        <v>63646.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1079505-43-CM26</t>
+          <t>895-80-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43733.36</v>
+        <v>4695.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3532-18-CM26</t>
+          <t>895-81-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1074.43</v>
+        <v>266.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079505-78-CM26</t>
+          <t>3532-169-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45193.32</v>
+        <v>55268.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>707418-26-SE26</t>
+          <t>1079505-1281-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,24 +1172,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>119497.68</v>
+        <v>38796.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2450-352-CM26</t>
+          <t>1079505-13-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32863.15</v>
+        <v>49177.93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2450-353-CM26</t>
+          <t>1079505-43-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>953.03</v>
+        <v>43733.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079505-134-CM26</t>
+          <t>3532-18-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>49358.2</v>
+        <v>1074.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1289649-18-CM26</t>
+          <t>1079505-78-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2965.19</v>
+        <v>45193.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1289649-19-CM26</t>
+          <t>707418-26-SE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1481,20 +1477,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11230.14</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2208-7-CM26</t>
+          <t>2450-352-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2200.95</v>
+        <v>32863.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>707418-61-CM26</t>
+          <t>2450-353-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5919.29</v>
+        <v>953.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079505-215-CM26</t>
+          <t>1079505-134-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>46086.2</v>
+        <v>49358.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079505-280-CM26</t>
+          <t>1289649-19-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>47255.86</v>
+        <v>11230.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079505-323-CM26</t>
+          <t>1289649-18-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>163.45</v>
+        <v>2965.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>973153-3-CM26</t>
+          <t>2208-7-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,28 +1854,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>546.1</v>
+        <v>2200.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079505-382-CM26</t>
+          <t>707418-61-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,43 +1915,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>48166.32</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2147-333-CM26</t>
+          <t>1079505-215-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,28 +1976,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5249.15</v>
+        <v>46086.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057438-174-CM26</t>
+          <t>1079505-280-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,28 +2037,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7124.76</v>
+        <v>47255.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>1079505-323-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>26168.7</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2147-359-CM26</t>
+          <t>973153-3-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SII Oficina de Bienestar</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14591.32</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>1079505-382-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17930.41</v>
+        <v>48166.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1395-590-CM26</t>
+          <t>2147-333-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>42411.12</v>
+        <v>5249.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1229788-160-CM26</t>
+          <t>1057438-174-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,22 +2302,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>23889.48</v>
+        <v>7124.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2125-1487-CM26</t>
+          <t>1660-651-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>74719.62</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2145-696-CM26</t>
+          <t>1057438-184-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,22 +2424,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>42727.74</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2146-385-CM26</t>
+          <t>2147-359-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12973.43</v>
+        <v>14591.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2147-386-CM26</t>
+          <t>1395-590-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5722.8</v>
+        <v>42411.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057438-237-CM26</t>
+          <t>1229788-160-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,27 +2602,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,6 +2647,311 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
+        <v>23889.48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2125-1487-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>74719.62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2145-696-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>42727.74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2146-385-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>12973.43</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2147-386-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>5722.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1057438-237-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>14477.85</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707418-1-CM25</t>
+          <t>1079505-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>35614.71</v>
+        <v>34477.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057440-268-CM25</t>
+          <t>707418-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>61394.11</v>
+        <v>35614.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>931-101-CM25</t>
+          <t>1057440-130-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3135.47</v>
+        <v>66529.92999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>895-53-CM25</t>
+          <t>1057440-268-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5929.04</v>
+        <v>61394.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079505-1021-CM25</t>
+          <t>3276-5-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>38551.55</v>
+        <v>21897.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079505-1159-CM25</t>
+          <t>1289649-20-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36230.73</v>
+        <v>14944.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3532-156-CM25</t>
+          <t>1079505-56-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>63646.74</v>
+        <v>30815.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>895-80-CM25</t>
+          <t>2554-1-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4695.42</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>895-81-CM25</t>
+          <t>2554-2-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>266.46</v>
+        <v>752.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3532-169-CM25</t>
+          <t>3532-9-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>55268.75</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079505-1281-CM25</t>
+          <t>1079505-183-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>38796.71</v>
+        <v>35184.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079505-13-CM26</t>
+          <t>2553-6-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>49177.93</v>
+        <v>1944.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1079505-43-CM26</t>
+          <t>2552-4-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>43733.36</v>
+        <v>3126.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3532-18-CM26</t>
+          <t>2554-10-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1074.43</v>
+        <v>2704.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1079505-78-CM26</t>
+          <t>2554-12-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45193.32</v>
+        <v>772.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>707418-26-SE26</t>
+          <t>1079505-279-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,24 +1477,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>119497.68</v>
+        <v>34714.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2450-352-CM26</t>
+          <t>2030-21-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.902.052-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>32863.15</v>
+        <v>281.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2450-353-CM26</t>
+          <t>707418-44-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>953.03</v>
+        <v>3784.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079505-134-CM26</t>
+          <t>1079505-420-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1646,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>49358.2</v>
+        <v>38788.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1289649-19-CM26</t>
+          <t>707418-54-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11230.14</v>
+        <v>9463.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1289649-18-CM26</t>
+          <t>953-165-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.511.040-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2965.19</v>
+        <v>2131.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2208-7-CM26</t>
+          <t>931-101-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2200.95</v>
+        <v>3135.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>707418-61-CM26</t>
+          <t>931-100-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5919.29</v>
+        <v>795.5700000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079505-215-CM26</t>
+          <t>1079505-538-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1951,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>46086.2</v>
+        <v>33552.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079505-280-CM26</t>
+          <t>973153-8-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>47255.86</v>
+        <v>338.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079505-323-CM26</t>
+          <t>973153-7-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,28 +2094,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>163.45</v>
+        <v>345.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>973153-3-CM26</t>
+          <t>3532-91-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,28 +2155,28 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>546.1</v>
+        <v>26466.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079505-382-CM26</t>
+          <t>1079505-620-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2195,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,43 +2216,43 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>48166.32</v>
+        <v>37687.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2147-333-CM26</t>
+          <t>2208-19-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,43 +2277,43 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5249.15</v>
+        <v>517.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057438-174-CM26</t>
+          <t>973153-10-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,28 +2338,28 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7124.76</v>
+        <v>219.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>1079505-763-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>26168.7</v>
+        <v>35746.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>697055-60-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,43 +2460,43 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>17930.41</v>
+        <v>436.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2147-359-CM26</t>
+          <t>1079505-913-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,43 +2521,43 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>14591.32</v>
+        <v>36083.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1395-590-CM26</t>
+          <t>707418-138-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,43 +2582,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>42411.12</v>
+        <v>28741.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1229788-160-CM26</t>
+          <t>707418-136-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,28 +2643,28 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>23889.48</v>
+        <v>3734.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2125-1487-CM26</t>
+          <t>1079505-967-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,28 +2704,28 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>74719.62</v>
+        <v>3405.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2145-696-CM26</t>
+          <t>895-53-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,28 +2765,28 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>42727.74</v>
+        <v>5929.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2146-385-CM26</t>
+          <t>1079505-1021-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,28 +2826,28 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12973.43</v>
+        <v>38551.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2147-386-CM26</t>
+          <t>3532-152-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,28 +2887,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5722.8</v>
+        <v>172.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057438-237-CM26</t>
+          <t>1079505-1159-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,7 +2948,2695 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
+        <v>36230.73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3532-156-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>81.925.500-8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>63646.74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>895-80-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>4695.42</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>895-81-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>266.46</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3532-169-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>81.925.500-8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>55268.75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1079505-1281-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>38796.71</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1079505-13-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>49177.93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1079505-43-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>43733.36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3532-18-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>81.925.500-8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1074.43</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1079505-78-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>45193.32</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>707418-26-SE26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>119497.68</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2450-352-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>32863.15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2450-353-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>953.03</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1079505-134-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>49358.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1289649-18-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>2965.19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1289649-19-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>11230.14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2208-7-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.803.000-k</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>2200.95</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>707418-61-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>5919.29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1079505-215-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>46086.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1079505-280-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>47255.86</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1079505-323-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>163.45</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>973153-3-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SII Oficina de Bienestar</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>546.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1079505-382-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>48166.32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2147-333-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>5249.15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1057438-174-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>7124.76</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1057438-184-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>17930.41</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2147-359-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>14591.32</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1660-651-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.606.408-8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>26168.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1395-590-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>42411.12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1229788-160-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>23889.48</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2125-1487-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>74719.62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2145-696-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>42727.74</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2146-385-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>12973.43</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1079505-463-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>48959.79</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2147-386-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>5722.8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1057438-233-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>7137.61</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2146-451-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>14665.43</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1660-751-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.606.408-8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>26977.21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1057438-237-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
         <v>14477.85</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2147-397-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>13667.31</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1229788-202-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>25827.57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1395-688-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>40696.68</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2125-1731-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>77044.88</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2145-809-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>29721.7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1057440-470-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>8725.440000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707418-1-CM25</t>
+          <t>1057440-130-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35614.71</v>
+        <v>66529.92999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057440-130-CM25</t>
+          <t>3276-5-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>66529.92999999999</v>
+        <v>21897.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057440-268-CM25</t>
+          <t>1289649-20-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>61394.11</v>
+        <v>14944.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3276-5-CM25</t>
+          <t>1079505-56-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21897.74</v>
+        <v>30815.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1289649-20-CM25</t>
+          <t>2554-1-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14944.84</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079505-56-CM25</t>
+          <t>2554-2-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30815.85</v>
+        <v>752.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2554-1-CM25</t>
+          <t>3532-9-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2619.84</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2554-2-CM25</t>
+          <t>1079505-183-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>752.64</v>
+        <v>35184.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3532-9-CM25</t>
+          <t>2553-6-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>965.88</v>
+        <v>1944.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079505-183-CM25</t>
+          <t>2552-4-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35184.62</v>
+        <v>3126.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2553-6-CM25</t>
+          <t>2554-12-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1944.49</v>
+        <v>772.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2552-4-CM25</t>
+          <t>2554-10-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3126.43</v>
+        <v>2704.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2554-10-CM25</t>
+          <t>1079505-279-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2704.59</v>
+        <v>34714.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2554-12-CM25</t>
+          <t>2030-21-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.902.052-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>772.74</v>
+        <v>281.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079505-279-CM25</t>
+          <t>707418-44-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>34714.11</v>
+        <v>3784.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2030-21-CM25</t>
+          <t>1079505-420-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.902.052-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>281.6</v>
+        <v>38788.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>707418-44-CM25</t>
+          <t>707418-54-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3784.54</v>
+        <v>9463.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079505-420-CM25</t>
+          <t>953-165-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.511.040-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38788.27</v>
+        <v>2131.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>707418-54-CM25</t>
+          <t>931-101-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9463.6</v>
+        <v>3135.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>953-165-CM25</t>
+          <t>931-100-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.511.040-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2131.56</v>
+        <v>795.5700000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>931-101-CM25</t>
+          <t>973153-7-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3135.47</v>
+        <v>345.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>931-100-CM25</t>
+          <t>1079505-538-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>795.5700000000001</v>
+        <v>33552.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079505-538-CM25</t>
+          <t>973153-8-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>33552.98</v>
+        <v>338.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>973153-8-CM25</t>
+          <t>3532-91-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>338.42</v>
+        <v>26466.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>973153-7-CM25</t>
+          <t>1079505-620-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>345.94</v>
+        <v>37687.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3532-91-CM25</t>
+          <t>2208-19-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26466.95</v>
+        <v>517.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079505-620-CM25</t>
+          <t>973153-10-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37687.59</v>
+        <v>219.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2208-19-CM25</t>
+          <t>1079505-763-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>517.2</v>
+        <v>35746.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>973153-10-CM25</t>
+          <t>697055-60-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>219.57</v>
+        <v>436.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1079505-763-CM25</t>
+          <t>1079505-913-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>35746.86</v>
+        <v>36083.85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>697055-60-CM25</t>
+          <t>707418-138-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>436.21</v>
+        <v>28741.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079505-913-CM25</t>
+          <t>707418-136-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>36083.85</v>
+        <v>3734.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>707418-138-CM25</t>
+          <t>1079505-967-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>28741.75</v>
+        <v>3405.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>707418-136-CM25</t>
+          <t>895-53-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3734.65</v>
+        <v>5929.04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079505-967-CM25</t>
+          <t>1079505-1021-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3405.15</v>
+        <v>38551.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>895-53-CM25</t>
+          <t>3532-152-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5929.04</v>
+        <v>172.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079505-1021-CM25</t>
+          <t>1079505-1159-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>38551.55</v>
+        <v>36230.73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3532-152-CM25</t>
+          <t>3532-156-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>172.05</v>
+        <v>63646.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1079505-1159-CM25</t>
+          <t>895-80-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>36230.73</v>
+        <v>4695.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3532-156-CM25</t>
+          <t>895-81-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>63646.74</v>
+        <v>266.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>895-80-CM25</t>
+          <t>3532-169-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4695.42</v>
+        <v>55268.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>895-81-CM25</t>
+          <t>1079505-1281-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>266.46</v>
+        <v>38796.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3532-169-CM25</t>
+          <t>1079505-13-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>55268.75</v>
+        <v>49177.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079505-1281-CM25</t>
+          <t>1079505-43-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>38796.71</v>
+        <v>43733.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079505-13-CM26</t>
+          <t>3532-18-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>49177.93</v>
+        <v>1074.43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079505-43-CM26</t>
+          <t>1079505-78-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>43733.36</v>
+        <v>45193.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3532-18-CM26</t>
+          <t>707418-26-SE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3429,20 +3429,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1074.43</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1079505-78-CM26</t>
+          <t>2450-352-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3456,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>45193.32</v>
+        <v>32863.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>707418-26-SE26</t>
+          <t>2450-353-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3517,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3551,24 +3555,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>119497.68</v>
+        <v>953.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2450-352-CM26</t>
+          <t>1079505-134-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>32863.15</v>
+        <v>49358.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2450-353-CM26</t>
+          <t>1289649-18-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>953.03</v>
+        <v>2965.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079505-134-CM26</t>
+          <t>1289649-19-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>49358.2</v>
+        <v>11230.14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1289649-18-CM26</t>
+          <t>2208-7-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2965.19</v>
+        <v>2200.95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1289649-19-CM26</t>
+          <t>707418-61-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11230.14</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2208-7-CM26</t>
+          <t>1079505-215-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2200.95</v>
+        <v>46086.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>707418-61-CM26</t>
+          <t>1079505-280-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5919.29</v>
+        <v>47255.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079505-215-CM26</t>
+          <t>1079505-323-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,18 +4050,18 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>46086.2</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079505-280-CM26</t>
+          <t>973153-3-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,28 +4111,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>47255.86</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079505-323-CM26</t>
+          <t>1079505-382-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>163.45</v>
+        <v>48166.32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>973153-3-CM26</t>
+          <t>2147-333-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>546.1</v>
+        <v>5249.15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1079505-382-CM26</t>
+          <t>1057438-174-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>48166.32</v>
+        <v>7124.76</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2147-333-CM26</t>
+          <t>1057438-184-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,22 +4315,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5249.15</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057438-174-CM26</t>
+          <t>2147-359-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,22 +4376,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7124.76</v>
+        <v>14591.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>1660-651-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>17930.41</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2147-359-CM26</t>
+          <t>1395-590-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>14591.32</v>
+        <v>42411.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>1229788-160-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,22 +4559,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>26168.7</v>
+        <v>23889.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1395-590-CM26</t>
+          <t>2125-1487-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4625,17 +4625,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>42411.12</v>
+        <v>74719.62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1229788-160-CM26</t>
+          <t>2145-696-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>23889.48</v>
+        <v>42727.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2125-1487-CM26</t>
+          <t>2146-385-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>74719.62</v>
+        <v>12973.43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2145-696-CM26</t>
+          <t>1079505-463-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,27 +4798,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>42727.74</v>
+        <v>48959.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2146-385-CM26</t>
+          <t>2147-386-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>12973.43</v>
+        <v>5722.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079505-463-CM26</t>
+          <t>1057438-233-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>48959.79</v>
+        <v>7137.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2147-386-CM26</t>
+          <t>2146-451-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5722.8</v>
+        <v>14665.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057438-233-CM26</t>
+          <t>1660-751-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7137.61</v>
+        <v>26977.21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2146-451-CM26</t>
+          <t>1057438-237-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>14665.43</v>
+        <v>14477.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1660-751-CM26</t>
+          <t>2147-397-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26977.21</v>
+        <v>13667.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057438-237-CM26</t>
+          <t>1229788-202-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14477.85</v>
+        <v>25827.57</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2147-397-CM26</t>
+          <t>1395-688-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>13667.31</v>
+        <v>40696.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1229788-202-CM26</t>
+          <t>2125-1731-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5357,17 +5357,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>25827.57</v>
+        <v>77044.88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1395-688-CM26</t>
+          <t>2145-809-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>40696.68</v>
+        <v>29721.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2125-1731-CM26</t>
+          <t>1057440-470-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,22 +5474,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>77044.88</v>
+        <v>8725.440000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2145-809-CM26</t>
+          <t>1079505-555-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>29721.7</v>
+        <v>46857.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057440-470-CM26</t>
+          <t>2146-494-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,27 +5591,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,7 +5636,678 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8725.440000000001</v>
+        <v>3124.96</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1057438-255-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>7318.88</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2147-437-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>5029.84</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1057440-502-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>11229.41</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1660-857-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.606.408-8</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>25863.74</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1057438-271-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>17167.72</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1395-773-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>41518</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1229788-255-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>24512.06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2147-478-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>14574.13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2125-1927-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>68027.37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2145-920-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>30397.96</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2146-528-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>13921.19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4462,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4527,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4592,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4657,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4722,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4787,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4852,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4917,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4982,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5047,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5177,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5242,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5307,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5372,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5437,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5502,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5567,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5632,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5697,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5762,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5957,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +6022,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6477,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6542,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6607,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6672,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>1660-651-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17930.41</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="65">
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>1057438-184-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>26168.7</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="67">
@@ -4804,7 +4804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1229788-160-CM26</t>
+          <t>2125-1487-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>23889.48</v>
+        <v>74719.62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2125-1487-CM26</t>
+          <t>2145-696-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>74719.62</v>
+        <v>42727.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2145-696-CM26</t>
+          <t>1229788-160-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>42727.74</v>
+        <v>23889.48</v>
       </c>
     </row>
     <row r="71">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2147-397-CM26</t>
+          <t>1395-688-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13667.31</v>
+        <v>40696.68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1229788-202-CM26</t>
+          <t>2147-397-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5539,17 +5539,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>25827.57</v>
+        <v>13667.31</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1395-688-CM26</t>
+          <t>1229788-202-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>40696.68</v>
+        <v>25827.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2125-1731-CM26</t>
+          <t>2145-809-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>77044.88</v>
+        <v>29721.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2145-809-CM26</t>
+          <t>2125-1731-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>29721.7</v>
+        <v>77044.88</v>
       </c>
     </row>
     <row r="83">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1395-773-CM26</t>
+          <t>2147-478-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>41518</v>
+        <v>14574.13</v>
       </c>
     </row>
     <row r="92">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2147-478-CM26</t>
+          <t>1395-773-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14574.13</v>
+        <v>41518</v>
       </c>
     </row>
     <row r="94">
@@ -6559,7 +6559,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2145-920-CM26</t>
+          <t>2146-528-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>30397.96</v>
+        <v>13921.19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2146-528-CM26</t>
+          <t>2145-920-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6644,46 +6644,436 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>30397.96</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1079505-653-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>45101.9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2146-553-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>3358.54</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2147-519-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>61.606.405-3</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>13921.19</v>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>4413.62</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1057438-299-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>6731.87</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1079505-671-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>1880.15</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1079505-662-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>1409.12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057440-130-CM25</t>
+          <t>707418-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>66529.92999999999</v>
+        <v>35614.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3276-5-CM25</t>
+          <t>1057440-130-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21897.74</v>
+        <v>66529.92999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1289649-20-CM25</t>
+          <t>1057440-268-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14944.84</v>
+        <v>61394.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079505-56-CM25</t>
+          <t>3276-5-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30815.85</v>
+        <v>21897.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2554-1-CM25</t>
+          <t>1289649-20-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2619.84</v>
+        <v>14944.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2554-2-CM25</t>
+          <t>1079505-56-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>752.64</v>
+        <v>30815.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3532-9-CM25</t>
+          <t>2554-1-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>965.88</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079505-183-CM25</t>
+          <t>2554-2-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35184.62</v>
+        <v>752.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2553-6-CM25</t>
+          <t>3532-9-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1944.49</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2552-4-CM25</t>
+          <t>1079505-183-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3126.43</v>
+        <v>35184.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2554-12-CM25</t>
+          <t>2553-6-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>772.74</v>
+        <v>1944.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2554-10-CM25</t>
+          <t>2552-4-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2704.59</v>
+        <v>3126.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079505-279-CM25</t>
+          <t>2554-12-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34714.11</v>
+        <v>772.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2030-21-CM25</t>
+          <t>2554-10-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.902.052-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>281.6</v>
+        <v>2704.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>707418-44-CM25</t>
+          <t>1079505-279-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3784.54</v>
+        <v>34714.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079505-420-CM25</t>
+          <t>2030-21-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.902.052-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38788.27</v>
+        <v>281.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>707418-54-CM25</t>
+          <t>707418-44-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9463.6</v>
+        <v>3784.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>953-165-CM25</t>
+          <t>1079505-420-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.511.040-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2131.56</v>
+        <v>38788.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>931-101-CM25</t>
+          <t>707418-54-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3135.47</v>
+        <v>9463.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>931-100-CM25</t>
+          <t>953-165-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.511.040-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>795.5700000000001</v>
+        <v>2131.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>973153-7-CM25</t>
+          <t>931-101-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,27 +1889,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>345.94</v>
+        <v>3135.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079505-538-CM25</t>
+          <t>931-100-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>33552.98</v>
+        <v>795.5700000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>973153-8-CM25</t>
+          <t>973153-7-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>338.42</v>
+        <v>345.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3532-91-CM25</t>
+          <t>1079505-538-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26466.95</v>
+        <v>33552.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079505-620-CM25</t>
+          <t>973153-8-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,27 +2149,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>37687.59</v>
+        <v>338.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2208-19-CM25</t>
+          <t>3532-91-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>517.2</v>
+        <v>26466.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>973153-10-CM25</t>
+          <t>1079505-620-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2284,22 +2284,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>219.57</v>
+        <v>37687.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079505-763-CM25</t>
+          <t>2208-19-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>35746.86</v>
+        <v>517.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>697055-60-CM25</t>
+          <t>973153-10-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,27 +2409,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>436.21</v>
+        <v>219.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1079505-913-CM25</t>
+          <t>1079505-763-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36083.85</v>
+        <v>35746.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>707418-138-CM25</t>
+          <t>697055-60-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>28741.75</v>
+        <v>436.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>707418-136-CM25</t>
+          <t>1079505-913-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3734.65</v>
+        <v>36083.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1079505-967-CM25</t>
+          <t>707418-138-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3405.15</v>
+        <v>28741.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>895-53-CM25</t>
+          <t>707418-136-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5929.04</v>
+        <v>3734.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079505-1021-CM25</t>
+          <t>1079505-967-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>38551.55</v>
+        <v>3405.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3532-152-CM25</t>
+          <t>895-53-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,27 +2864,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>172.05</v>
+        <v>5929.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079505-1159-CM25</t>
+          <t>1079505-1021-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>36230.73</v>
+        <v>38551.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3532-156-CM25</t>
+          <t>3532-152-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>63646.74</v>
+        <v>172.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>895-80-CM25</t>
+          <t>1079505-1159-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4695.42</v>
+        <v>36230.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>895-81-CM25</t>
+          <t>3532-156-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,27 +3124,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>266.46</v>
+        <v>63646.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3532-169-CM25</t>
+          <t>895-80-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3194,22 +3194,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>55268.75</v>
+        <v>4695.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079505-1281-CM25</t>
+          <t>895-81-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3259,22 +3259,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>38796.71</v>
+        <v>266.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1079505-13-CM26</t>
+          <t>3532-169-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>49177.93</v>
+        <v>55268.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079505-43-CM26</t>
+          <t>1079505-1281-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>43733.36</v>
+        <v>38796.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3532-18-CM26</t>
+          <t>1079505-13-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1074.43</v>
+        <v>49177.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079505-78-CM26</t>
+          <t>1079505-43-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45193.32</v>
+        <v>43733.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>707418-26-SE26</t>
+          <t>3532-18-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>119497.68</v>
+        <v>1074.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2450-352-CM26</t>
+          <t>1079505-78-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>32863.15</v>
+        <v>45193.32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2450-353-CM26</t>
+          <t>707418-26-SE26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>953.03</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079505-134-CM26</t>
+          <t>2450-353-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>49358.2</v>
+        <v>953.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1289649-18-CM26</t>
+          <t>2450-352-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2965.19</v>
+        <v>32863.15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1289649-19-CM26</t>
+          <t>1079505-134-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11230.14</v>
+        <v>49358.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2208-7-CM26</t>
+          <t>1289649-19-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2200.95</v>
+        <v>11230.14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>707418-61-CM26</t>
+          <t>1289649-18-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5919.29</v>
+        <v>2965.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079505-215-CM26</t>
+          <t>2208-7-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>46086.2</v>
+        <v>2200.95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079505-280-CM26</t>
+          <t>707418-61-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>47255.86</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079505-323-CM26</t>
+          <t>1079505-215-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4278,18 +4278,18 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>163.45</v>
+        <v>46086.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>973153-3-CM26</t>
+          <t>1079505-280-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,28 +4343,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>546.1</v>
+        <v>47255.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079505-382-CM26</t>
+          <t>1079505-323-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>48166.32</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2147-333-CM26</t>
+          <t>973153-3-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5249.15</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057438-174-CM26</t>
+          <t>1079505-382-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7124.76</v>
+        <v>48166.32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1660-651-CM26</t>
+          <t>2147-333-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>26168.7</v>
+        <v>5249.15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2147-359-CM26</t>
+          <t>1057438-174-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4624,22 +4624,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>14591.32</v>
+        <v>7124.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057438-184-CM26</t>
+          <t>1660-651-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>17930.41</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1395-590-CM26</t>
+          <t>1057438-184-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>42411.12</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2125-1487-CM26</t>
+          <t>2147-359-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>74719.62</v>
+        <v>14591.32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2145-696-CM26</t>
+          <t>1395-590-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>42727.74</v>
+        <v>42411.12</v>
       </c>
     </row>
     <row r="70">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2146-385-CM26</t>
+          <t>2125-1487-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>12973.43</v>
+        <v>74719.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1079505-463-CM26</t>
+          <t>2145-696-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>48959.79</v>
+        <v>42727.74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2147-386-CM26</t>
+          <t>2146-385-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5722.8</v>
+        <v>12973.43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057438-233-CM26</t>
+          <t>1079505-463-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7137.61</v>
+        <v>48959.79</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2146-451-CM26</t>
+          <t>2147-386-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>14665.43</v>
+        <v>5722.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1660-751-CM26</t>
+          <t>1057438-233-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26977.21</v>
+        <v>7137.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057438-237-CM26</t>
+          <t>2146-451-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>14477.85</v>
+        <v>14665.43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1395-688-CM26</t>
+          <t>1660-751-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>40696.68</v>
+        <v>26977.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2147-397-CM26</t>
+          <t>1057438-237-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13667.31</v>
+        <v>14477.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1229788-202-CM26</t>
+          <t>2147-397-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>25827.57</v>
+        <v>13667.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2145-809-CM26</t>
+          <t>1229788-202-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>29721.7</v>
+        <v>25827.57</v>
       </c>
     </row>
     <row r="82">
@@ -5779,7 +5779,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057440-470-CM26</t>
+          <t>1395-688-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5794,22 +5794,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8725.440000000001</v>
+        <v>40696.68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1079505-555-CM26</t>
+          <t>2145-809-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>46857.71</v>
+        <v>29721.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2146-494-CM26</t>
+          <t>1057440-470-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3124.96</v>
+        <v>8725.440000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1057438-255-CM26</t>
+          <t>1079505-555-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7318.88</v>
+        <v>46857.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2147-437-CM26</t>
+          <t>2146-494-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5029.84</v>
+        <v>3124.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057440-502-CM26</t>
+          <t>1057438-255-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6119,22 +6119,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>11229.41</v>
+        <v>7318.88</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1660-857-CM26</t>
+          <t>2147-437-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>25863.74</v>
+        <v>5029.84</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057438-271-CM26</t>
+          <t>1057440-502-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6249,22 +6249,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>17167.72</v>
+        <v>11229.41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2147-478-CM26</t>
+          <t>1660-857-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>14574.13</v>
+        <v>25863.74</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1229788-255-CM26</t>
+          <t>1057438-271-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>24512.06</v>
+        <v>17167.72</v>
       </c>
     </row>
     <row r="93">
@@ -6494,7 +6494,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2125-1927-CM26</t>
+          <t>1229788-255-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>68027.37</v>
+        <v>24512.06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2146-528-CM26</t>
+          <t>2147-478-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>13921.19</v>
+        <v>14574.13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2145-920-CM26</t>
+          <t>2125-1927-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>30397.96</v>
+        <v>68027.37</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1079505-653-CM26</t>
+          <t>2146-528-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>45101.9</v>
+        <v>13921.19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2146-553-CM26</t>
+          <t>2145-920-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3358.54</v>
+        <v>30397.96</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2147-519-CM26</t>
+          <t>1079505-653-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6834,22 +6834,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4413.62</v>
+        <v>45101.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057438-299-CM26</t>
+          <t>2146-553-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6731.87</v>
+        <v>3358.54</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1079505-671-CM26</t>
+          <t>2147-519-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7008,72 +7008,202 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1880.15</v>
+        <v>4413.62</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>1057438-299-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>6731.87</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>1079505-662-CM26</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>60.505.206-1</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
         <v>1409.12</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1079505-671-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>1880.15</v>
       </c>
     </row>
   </sheetData>
